--- a/exports/colleges/10720_maulana-azad-medical-college-mamc-new-delhi.xlsx
+++ b/exports/colleges/10720_maulana-azad-medical-college-mamc-new-delhi.xlsx
@@ -607,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -619,7 +619,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -714,7 +714,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>MBBS + NEETPG</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>17 Apr - 07 Jul 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MBBS</t>
+          <t>M.B.B.S.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -766,17 +766,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>M.B.B.S.</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>12900</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5 Years 6 Months</t>
+          <t>5 years 6 months</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -786,17 +786,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10+2 + NEET UG</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NEET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>12 Aug - 20 Aug 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>Master of Surgery [M.S]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Master of Surgery [M.S]</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Graduation + NEET PG</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NEET PG</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>17 Apr - 07 Jul 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Graduation + NEET PG</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>17 Apr - 07 Jul 2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.03 Lakhs</t>
+          <t>1.03 L</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Post Graduation + NEET SS</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1004,27 +1004,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M.D</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>M.D</t>
+          <t>Doctor of Medicine [MD]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>M.D</t>
+          <t>Doctor of Medicine [MD]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>₹ 72,775</t>
+          <t>72,775</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Graduation + NEET PG</t>
+          <t>MBBS + NEETPG</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET PG</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1071,17 +1071,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MBBS</t>
+          <t>M.B.B.S.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MBBS</t>
+          <t>M.B.B.S.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>₹ 14,125</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1128,27 +1128,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M.S</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>M.S</t>
+          <t>Master of Surgery [M.S]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>M.S</t>
+          <t>Master of Surgery [M.S]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>₹ 72,775</t>
+          <t>72,775</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET PG</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1190,27 +1190,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M.Ch</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>M.Ch</t>
+          <t>Master of Surgery [MS] (Ophthalmology)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>M.Ch</t>
+          <t>Master of Surgery [MS] (Ophthalmology)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>₹ 1.03 Lakhs</t>
+          <t>72,775</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Post Graduation + NEET SS</t>
+          <t>Graduation + NEET PG</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET PG</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1252,27 +1252,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PG Diploma</t>
+          <t>M.Ch</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PG Diploma</t>
+          <t>Master of Chirurgiae [M.Ch] (Paediatric Surgery)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PG Diploma</t>
+          <t>Master of Chirurgiae [M.Ch] (Paediatric Surgery)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>₹ 56,875</t>
+          <t>1.03 Lakhs</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Graduation</t>
+          <t>Post Graduation + NEET SS</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET SS</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1314,22 +1314,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>M.D</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>M.D</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>M.D</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>₹ 47,700</t>
+          <t>₹ 72,775</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + NEET PG</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1376,27 +1376,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Caution Fee</t>
+          <t>MBBS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Caution Fee</t>
+          <t>MBBS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Caution Fee</t>
+          <t>MBBS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>₹ 25,000</t>
+          <t>₹ 14,125</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>5 Years 6 Months</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 + NEET UG</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1438,22 +1438,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Miscellaneous Fee</t>
+          <t>M.S</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Miscellaneous Fee</t>
+          <t>M.S</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Miscellaneous Fee</t>
+          <t>M.S</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>₹ 75</t>
+          <t>₹ 72,775</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + NEET PG</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>M.Ch</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>M.Ch</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>M.Ch</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>₹ 72,775</t>
+          <t>₹ 1.03 Lakhs</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Post Graduation + NEET SS</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET SS</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1562,27 +1562,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tuition Fees</t>
+          <t>PG Diploma</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tuition Fees</t>
+          <t>PG Diploma</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tuition Fees</t>
+          <t>PG Diploma</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>₹15900</t>
+          <t>₹ 56,875</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Year</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1624,22 +1624,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Caution Fee *</t>
+          <t>Paediatrics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Caution Fee *</t>
+          <t>Paediatrics</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Caution Fee *</t>
+          <t>Paediatrics</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>₹25000</t>
+          <t>₹ 56,875</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1686,22 +1686,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Miscellaneous Fees</t>
+          <t>Obstetrics &amp; Gynaecology</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Miscellaneous Fees</t>
+          <t>Obstetrics &amp; Gynaecology</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Miscellaneous Fees</t>
+          <t>Obstetrics &amp; Gynaecology</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>₹75</t>
+          <t>₹ 56,875</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1748,22 +1748,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Yearly Fees</t>
+          <t>Anaesthesia</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yearly Fees</t>
+          <t>Anaesthesia</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Yearly Fees</t>
+          <t>Anaesthesia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>₹40975</t>
+          <t>₹ 56,875</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Dermatology, Venereology &amp; Leprosy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Dermatology, Venereology &amp; Leprosy</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Dermatology, Venereology &amp; Leprosy</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>₹ 12,125</t>
+          <t>₹ 56,875</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1872,22 +1872,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>E.N.T.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>E.N.T.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>E.N.T.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>₹ 14,125</t>
+          <t>₹ 56,875</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1934,22 +1934,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Ophthalmology</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Ophthalmology</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Ophthalmology</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>₹ 77,700</t>
+          <t>₹ 56,875</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1983,688 +1983,6 @@
         </is>
       </c>
       <c r="L22" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>10720</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Total Fee</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Total Fee</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Total Fee</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>₹ 1.03 Lakhs</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>10720</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Tuition Fees</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Tuition Fees</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Tuition Fees</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>₹25900</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>10720</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Yearly Fees</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Yearly Fees</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Yearly Fees</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>₹50975</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>10720</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Tuition Fee</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Tuition Fee</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Tuition Fee</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>₹ 31,800</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>10720</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Total Fee</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Total Fee</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Total Fee</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>₹ 56,875</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>10720</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Paediatrics</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Paediatrics</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Paediatrics</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>₹ 56,875</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Graduation</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>10720</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Obstetrics &amp; Gynaecology</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Obstetrics &amp; Gynaecology</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Obstetrics &amp; Gynaecology</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>₹ 56,875</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Graduation</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>10720</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Anaesthesia</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Anaesthesia</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Anaesthesia</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>₹ 56,875</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Graduation</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>10720</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Dermatology, Venereology &amp; Leprosy</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Dermatology, Venereology &amp; Leprosy</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Dermatology, Venereology &amp; Leprosy</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>₹ 56,875</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Graduation</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>10720</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>E.N.T.</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>E.N.T.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>E.N.T.</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>₹ 56,875</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Graduation</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>10720</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Ophthalmology</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ophthalmology</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Ophthalmology</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>₹ 56,875</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Graduation</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
         <is>
           <t>UG</t>
         </is>
